--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487586_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487586_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7298</v>
+        <v>5.7462</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3382</v>
+        <v>3.4363</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3916</v>
+        <v>2.3099</v>
       </c>
       <c r="G2" t="n">
         <v>2.7402</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>3.318</v>
+        <v>1.3344</v>
       </c>
       <c r="T2" t="n">
-        <v>3.46</v>
+        <v>1.5581</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1419</v>
+        <v>-0.2237</v>
       </c>
       <c r="V2" t="n">
         <v>2.4477</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.907</v>
+        <v>3.158</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0166</v>
+        <v>3.2104</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1096</v>
+        <v>-0.0524</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7623</v>
+        <v>3.2851</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5126</v>
+        <v>1.3882</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2497</v>
+        <v>1.8969</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9036</v>
+        <v>2.9914</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0134</v>
+        <v>1.0834</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8903</v>
+        <v>1.908</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1413</v>
+        <v>0.2937</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4992</v>
+        <v>0.3048</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6406</v>
+        <v>-0.0111</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S3" t="n">
-        <v>0.891</v>
+        <v>-0.2913</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5473</v>
+        <v>-0.0631</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3437</v>
+        <v>-0.2282</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2239</v>
+        <v>-0.6119</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7759</v>
+        <v>2.3525</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9101</v>
+        <v>2.8164</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1342</v>
+        <v>-0.4639</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2851</v>
+        <v>1.7623</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3882</v>
+        <v>1.5126</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8969</v>
+        <v>0.2497</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9914</v>
+        <v>2.9036</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0834</v>
+        <v>1.0134</v>
       </c>
       <c r="L4" t="n">
-        <v>1.908</v>
+        <v>1.8903</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2937</v>
+        <v>-1.1413</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3048</v>
+        <v>0.4992</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0111</v>
+        <v>-1.6406</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6734</v>
+        <v>0.3365</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3634</v>
+        <v>0.3471</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.31</v>
+        <v>-0.0106</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6119</v>
+        <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2751</v>
+        <v>0.1615</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1523</v>
+        <v>-1.852</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8772</v>
+        <v>2.0135</v>
       </c>
       <c r="G5" t="n">
         <v>-1.8393</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.406</v>
+        <v>0.0306</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.3631</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4688</v>
+        <v>-0.3325</v>
       </c>
       <c r="V5" t="n">
         <v>0.6119</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8165</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9155</v>
+        <v>-2.3299</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7319</v>
+        <v>1.4907</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3203</v>
+        <v>-0.8723</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0017</v>
+        <v>-3.0195</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3219</v>
+        <v>2.1471</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0653</v>
+        <v>-2.2222</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0247</v>
+        <v>-2.9123</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0406</v>
+        <v>0.6901</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3856</v>
+        <v>1.3499</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0231</v>
+        <v>-0.1071</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3625</v>
+        <v>1.457</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>1.262</v>
+        <v>-0.549</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8203</v>
+        <v>-0.1077</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5583</v>
+        <v>-0.4413</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2749</v>
+        <v>-0.9741</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4146</v>
+        <v>0.4256</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1397</v>
+        <v>-1.3997</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2325</v>
+        <v>-0.0538</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6986</v>
+        <v>2.0349</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5339</v>
+        <v>-2.0888</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2935</v>
+        <v>0.2433</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6261</v>
+        <v>2.2986</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6673</v>
+        <v>-2.0553</v>
       </c>
       <c r="M7" t="n">
-        <v>0.061</v>
+        <v>-0.2971</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0725</v>
+        <v>-0.2637</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1335</v>
+        <v>-0.0334</v>
       </c>
       <c r="P7" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2364</v>
+        <v>-0.5308</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1211</v>
+        <v>0.2778</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1153</v>
+        <v>-0.8086</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5537</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.0955</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4023</v>
+        <v>-1.2476</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2751</v>
+        <v>-1.4146</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1271</v>
+        <v>0.167</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0538</v>
+        <v>-1.2325</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0349</v>
+        <v>-0.6986</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0888</v>
+        <v>-0.5339</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2433</v>
+        <v>-1.2935</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2986</v>
+        <v>-0.6261</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0553</v>
+        <v>-0.6673</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2971</v>
+        <v>0.061</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2637</v>
+        <v>-0.0725</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0334</v>
+        <v>0.1335</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9589</v>
+        <v>-0.2092</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4229</v>
+        <v>-0.1211</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5361</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5537</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0955</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4493</v>
+        <v>-1.4537</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1307</v>
+        <v>0.1147</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6814</v>
+        <v>-1.5684</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8723</v>
+        <v>-1.3203</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0195</v>
+        <v>0.0017</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1471</v>
+        <v>-1.3219</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2222</v>
+        <v>0.0653</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.9123</v>
+        <v>0.0247</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6901</v>
+        <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3499</v>
+        <v>-1.3856</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1071</v>
+        <v>-0.0231</v>
       </c>
       <c r="O9" t="n">
-        <v>1.457</v>
+        <v>-1.3625</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.159</v>
+        <v>0.6247</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9085</v>
+        <v>1.0195</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2505</v>
+        <v>-0.3948</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>G. MORENO ABAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3588</v>
+        <v>-2.4363</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7075</v>
+        <v>-2.3862</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3487</v>
+        <v>-0.0501</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8879</v>
+        <v>-1.0871</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2579</v>
+        <v>0.0091</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.63</v>
+        <v>-1.0961</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8596</v>
+        <v>-1.1923</v>
       </c>
       <c r="K10" t="n">
         <v>-0.6467000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2129</v>
+        <v>-0.5455</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0282</v>
+        <v>0.1052</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3889</v>
+        <v>0.6558</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4171</v>
+        <v>-0.5506</v>
       </c>
       <c r="P10" t="n">
         <v>-0.7761</v>
@@ -1234,28 +1234,28 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0725</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1222</v>
+        <v>-0.2238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1947</v>
+        <v>-0.3494</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MORENO ABAD</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8273</v>
+        <v>-2.6046</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5864</v>
+        <v>-3.0078</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2409</v>
+        <v>0.4032</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0871</v>
+        <v>-1.8879</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0091</v>
+        <v>-0.2579</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0961</v>
+        <v>-1.63</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1923</v>
+        <v>-1.8596</v>
       </c>
       <c r="K11" t="n">
         <v>-0.6467000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5455</v>
+        <v>-1.2129</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1052</v>
+        <v>-0.0282</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6558</v>
+        <v>0.3889</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5506</v>
+        <v>-0.4171</v>
       </c>
       <c r="P11" t="n">
         <v>-0.7761</v>
@@ -1312,22 +1312,22 @@
         <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9641</v>
+        <v>-0.3182</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.424</v>
+        <v>-0.1781</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5401</v>
+        <v>-0.1402</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5423</v>
+        <v>-4.3961</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.455</v>
+        <v>-4.5541</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0873</v>
+        <v>0.158</v>
       </c>
       <c r="G12" t="n">
         <v>0.1748</v>
@@ -1390,13 +1390,13 @@
         <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9708</v>
+        <v>-0.8246</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9691</v>
+        <v>-0.0682</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0018</v>
+        <v>-0.7565</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.533799999999999</v>
+        <v>-2.533400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.541200000000002</v>
+        <v>-5.541200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0076</v>
+        <v>3.0078</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3307999999999992</v>
+        <v>-0.3308</v>
       </c>
       <c r="H13" t="n">
         <v>1.0875</v>
@@ -1441,13 +1441,13 @@
         <v>-1.4183</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.736</v>
+        <v>-2.735999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>-0.2057000000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.529999999999999</v>
+        <v>-2.53</v>
       </c>
       <c r="M13" t="n">
         <v>2.4054</v>
@@ -1468,7 +1468,7 @@
         <v>7.761199999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9701000000000009</v>
+        <v>-0.9700000000000002</v>
       </c>
       <c r="T13" t="n">
         <v>2.8036</v>
@@ -1480,7 +1480,7 @@
         <v>0.7074</v>
       </c>
       <c r="W13" t="n">
-        <v>4.092499999999999</v>
+        <v>4.0925</v>
       </c>
       <c r="X13" t="n">
         <v>-3.3851</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. ALMENARA AMADOR</t>
+          <t>G. ARTILES ROMERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1562</v>
+        <v>2.7893</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5507</v>
+        <v>1.1815</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6055</v>
+        <v>1.6078</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7625</v>
+        <v>2.0049</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8609</v>
+        <v>1.193</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0984</v>
+        <v>0.8119</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8979</v>
+        <v>1.7168</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7127</v>
+        <v>0.3543</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1852</v>
+        <v>1.3625</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1354</v>
+        <v>0.2881</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1483</v>
+        <v>0.8387</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2836</v>
+        <v>-0.5506</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1546,28 +1546,28 @@
         <v>0.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7817</v>
+        <v>1.0187</v>
       </c>
       <c r="T14" t="n">
-        <v>0.729</v>
+        <v>0.4349</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0527</v>
+        <v>0.5838</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6119</v>
+        <v>-0.2343</v>
       </c>
       <c r="W14" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2821</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. ARTILES ROMERO</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8244</v>
+        <v>2.3118</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0804</v>
+        <v>1.4465</v>
       </c>
       <c r="F15" t="n">
-        <v>1.744</v>
+        <v>0.8653</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0049</v>
+        <v>1.6438</v>
       </c>
       <c r="H15" t="n">
-        <v>1.193</v>
+        <v>0.8964</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8119</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7168</v>
+        <v>1.268</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3543</v>
+        <v>0.6262</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3625</v>
+        <v>0.6418</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2881</v>
+        <v>0.3758</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8387</v>
+        <v>0.2702</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5506</v>
+        <v>0.1056</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9702</v>
+        <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0538</v>
+        <v>0.3337</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6662</v>
+        <v>0.7845</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7201</v>
+        <v>-0.4508</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2343</v>
+        <v>1.6925</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.3044</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2343</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>D. ALMENARA AMADOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3841</v>
+        <v>1.8197</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8459</v>
+        <v>1.3505</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5382</v>
+        <v>0.4692</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6438</v>
+        <v>0.7625</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8964</v>
+        <v>0.8609</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7475000000000001</v>
+        <v>-0.0984</v>
       </c>
       <c r="J16" t="n">
-        <v>1.268</v>
+        <v>0.8979</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6262</v>
+        <v>0.7127</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6418</v>
+        <v>0.1852</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3758</v>
+        <v>-0.1354</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2702</v>
+        <v>0.1483</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1056</v>
+        <v>-0.2836</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3582</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.594</v>
+        <v>0.4453</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1839</v>
+        <v>0.5288</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7779</v>
+        <v>-0.0835</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6925</v>
+        <v>0.6119</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3044</v>
+        <v>0.894</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6119</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3702</v>
+        <v>1.3152</v>
       </c>
       <c r="E17" t="n">
-        <v>0.333</v>
+        <v>0.0327</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0373</v>
+        <v>1.2825</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2004</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1348</v>
+        <v>1.0798</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1635</v>
+        <v>0.4088</v>
       </c>
       <c r="V17" t="n">
         <v>0.6597</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9683</v>
+        <v>0.3521</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0075</v>
+        <v>-0.6335</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9758</v>
+        <v>0.9856</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5905</v>
+        <v>0.645</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7688</v>
+        <v>0.2752</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1784</v>
+        <v>0.3699</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5053</v>
+        <v>0.5365</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6271</v>
+        <v>1.3512</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1218</v>
+        <v>-0.8146</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9149</v>
+        <v>0.1085</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1417</v>
+        <v>-1.076</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0566</v>
+        <v>1.1845</v>
       </c>
       <c r="P18" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3647</v>
+        <v>-0.4974</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1859</v>
+        <v>0.1777</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8212</v>
+        <v>-0.6751</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>-0.3776</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3892</v>
+        <v>-0.4889</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0063</v>
+        <v>-0.7288</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3955</v>
+        <v>0.2399</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5103</v>
+        <v>-0.0369</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4352</v>
+        <v>0.3691</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0751</v>
+        <v>-0.406</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.766</v>
+        <v>-0.6261</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.969</v>
+        <v>0.0412</v>
       </c>
       <c r="L19" t="n">
-        <v>0.203</v>
+        <v>-0.6673</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2558</v>
+        <v>0.5893</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5339</v>
+        <v>0.3279</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2781</v>
+        <v>0.2614</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3472</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7597</v>
+        <v>-0.1026</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5875</v>
+        <v>-0.4553</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.024</v>
+        <v>-0.5389</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2341</v>
+        <v>-0.9072</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2581</v>
+        <v>0.3683</v>
       </c>
       <c r="G20" t="n">
-        <v>0.645</v>
+        <v>-1.5103</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2752</v>
+        <v>-1.4352</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3699</v>
+        <v>-0.0751</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5365</v>
+        <v>-1.766</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3512</v>
+        <v>-1.969</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8146</v>
+        <v>0.203</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1085</v>
+        <v>0.2558</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.076</v>
+        <v>0.5339</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1845</v>
+        <v>-0.2781</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8255</v>
+        <v>1.4191</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4229</v>
+        <v>0.8588</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4026</v>
+        <v>0.5602</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3776</v>
+        <v>-1.2239</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.833</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.929</v>
+        <v>-1.509</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2944</v>
+        <v>0.676</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0369</v>
+        <v>-0.5905</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3691</v>
+        <v>-1.7688</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.406</v>
+        <v>1.1784</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6261</v>
+        <v>-1.5053</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0412</v>
+        <v>-1.6271</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6673</v>
+        <v>0.1218</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5893</v>
+        <v>0.9149</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3279</v>
+        <v>-0.1417</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2614</v>
+        <v>1.0566</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7037</v>
+        <v>-0.4366</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3028</v>
+        <v>0.6844</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4008</v>
+        <v>-1.121</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X21" t="n">
         <v>-0.2821</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.8391</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8263</v>
+        <v>-1.4798</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5809</v>
+        <v>0.6407</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3434</v>
+        <v>0.5133</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0708</v>
+        <v>1.0471</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2725</v>
+        <v>-0.5339</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2801</v>
+        <v>-0.3254</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2801</v>
+        <v>1.0092</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.3347</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.8387</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.351</v>
+        <v>0.0379</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2725</v>
+        <v>0.8008</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8127</v>
+        <v>-0.7702</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5462</v>
+        <v>-0.1842</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2665</v>
+        <v>-0.586</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1666</v>
+        <v>-0.9234</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7801</v>
+        <v>-1.2974</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6135</v>
+        <v>0.374</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5133</v>
+        <v>-0.4873</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0471</v>
+        <v>-1.7219</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5339</v>
+        <v>1.2346</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3254</v>
+        <v>-1.5966</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0092</v>
+        <v>-1.5077</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3347</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8387</v>
+        <v>1.1093</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0379</v>
+        <v>-0.2142</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8008</v>
+        <v>1.3235</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0978</v>
+        <v>-1.2705</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4845</v>
+        <v>0.0171</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6133</v>
+        <v>-1.2875</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2761</v>
+        <v>-1.2094</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.889</v>
+        <v>0.4259</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3871</v>
+        <v>-1.6354</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0702</v>
+        <v>-0.3434</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4029</v>
+        <v>-0.0708</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6673</v>
+        <v>-0.2725</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.2801</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0206</v>
+        <v>0.2801</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4235</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4235</v>
+        <v>-0.351</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>-0.2725</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2326,28 +2326,28 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2059</v>
+        <v>0.3578</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2423</v>
+        <v>0.1458</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0363</v>
+        <v>0.212</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.751</v>
+        <v>-1.2216</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7979</v>
+        <v>-0.889</v>
       </c>
       <c r="F25" t="n">
-        <v>0.047</v>
+        <v>-0.3326</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4873</v>
+        <v>-1.0702</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7219</v>
+        <v>-0.4029</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2346</v>
+        <v>-0.6673</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.5966</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.5077</v>
+        <v>0.0206</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.6673</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1093</v>
+        <v>-0.4235</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2142</v>
+        <v>-0.4235</v>
       </c>
       <c r="O25" t="n">
-        <v>1.3235</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.098</v>
+        <v>-0.1514</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4834</v>
+        <v>-0.2423</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6146</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.533599999999999</v>
+        <v>2.5338</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0076</v>
+        <v>-3.007599999999999</v>
       </c>
       <c r="F26" t="n">
         <v>5.5413</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3305000000000003</v>
+        <v>0.3304999999999998</v>
       </c>
       <c r="H26" t="n">
         <v>-1.0874</v>
@@ -2464,10 +2464,10 @@
         <v>-1.1118</v>
       </c>
       <c r="M26" t="n">
-        <v>2.7359</v>
+        <v>2.735900000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2059000000000001</v>
+        <v>0.2059000000000002</v>
       </c>
       <c r="O26" t="n">
         <v>2.5301</v>
@@ -2482,13 +2482,13 @@
         <v>9.701799999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9700000000000002</v>
+        <v>0.9702999999999997</v>
       </c>
       <c r="T26" t="n">
-        <v>3.7739</v>
+        <v>3.773899999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8038</v>
+        <v>-2.8036</v>
       </c>
       <c r="V26" t="n">
         <v>-0.7076</v>
